--- a/assets/constructions/examples/ctd_tsmb_turn.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_turn.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,33 +619,50 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MC422BCR05L09RVTX</t>
+          <t>BTLR20.066221.RETC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Microscope</t>
-        </is>
-      </c>
+          <t>BRICE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VAR_MC4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
+          <t>VAR_M6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -653,45 +670,45 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.88</v>
+        <v>2.78</v>
       </c>
       <c r="M2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="O2" t="n">
+        <v>21</v>
+      </c>
+      <c r="P2" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.2</v>
       </c>
-      <c r="N2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="O2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P2" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.05</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>11.5</v>
+        <v>23.3</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -699,15 +716,15 @@
         <v>-8</v>
       </c>
       <c r="X2" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.7</v>
+        <v>49</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:6</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -717,12 +734,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -745,13 +762,32 @@
       <c r="AL2" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5322.49</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>5322.49</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L090.5-20/CN45F</t>
+          <t>L047.5-25/K10F</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -768,10 +804,14 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PMKS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>5</v>
       </c>
@@ -794,10 +834,10 @@
         <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="n">
         <v>0.5</v>
@@ -814,10 +854,10 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="X3" t="n">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
@@ -833,12 +873,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>CN45F</t>
+          <t>K10F</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>TIN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -861,13 +901,32 @@
       <c r="AL3" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>4751.13</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L090.5-15/CN45F</t>
+          <t>L050.3-20/CN45F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -889,37 +948,37 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -939,7 +998,7 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>DUEM_DCON:5</t>
+          <t>DUEM_DCON:4</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -977,85 +1036,86 @@
       <c r="AL4" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>4742.86</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L050.5-10/AL41F</t>
+          <t>MPR1.5R0.1L6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DUEMMEL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ULTRAMINI</t>
-        </is>
-      </c>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.4</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>20</v>
-      </c>
-      <c r="X5" t="n">
-        <v>110</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>DUEM_DCON:5</t>
+          <t>DER_DCON:4</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1063,14 +1123,10 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>AL41F</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -1092,90 +1148,109 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Ultramini.pdf</t>
+          <t>DEREK Micro Boring. Инструмент для обработки отверстий малых диаметров.</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R090.3-10/XC2A</t>
+          <t>M442BCR05L16RVTX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DUEMMEL</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ULTRAMINI</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>Microscope</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VAR_M4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>35.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>18.2</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>20</v>
+        <v>-8</v>
       </c>
       <c r="X6" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>21</v>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>DUEM_DCON:4</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1185,12 +1260,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>XC2A</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -1212,7 +1287,26 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Ultramini.pdf</t>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>3142.29</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
